--- a/table/resources/sample/PloygameRoom.xlsx
+++ b/table/resources/sample/PloygameRoom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PloygameRoom" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>id</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>HILLO</t>
+  </si>
+  <si>
+    <t>空袭</t>
   </si>
 </sst>
 </file>
@@ -1674,6 +1677,38 @@
         <v>9600</v>
       </c>
     </row>
+    <row r="8" ht="16.5" spans="1:16">
+      <c r="A8">
+        <v>4004001</v>
+      </c>
+      <c r="B8">
+        <v>400400</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>400400001</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="11">
+        <v>10000000</v>
+      </c>
+      <c r="I8">
+        <v>9500</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
     <row r="13" ht="16.5" spans="1:16">
       <c r="F13" s="20"/>
     </row>

--- a/table/resources/sample/PloygameRoom.xlsx
+++ b/table/resources/sample/PloygameRoom.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\ploygame\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9790DF78-45C0-4BDA-999B-C7AFC920CD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="PloygameRoom" sheetId="1" r:id="rId1"/>
@@ -33,19 +27,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>g8s8chenkaijia</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1 普通场 
@@ -55,40 +48,37 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>单位：分（换成元则除100)</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最大押分值*10000</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{E280FC3D-69A9-4F71-A8BD-66FF8E56E03D}">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -97,7 +87,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -106,14 +95,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -122,7 +110,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -132,14 +119,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -148,7 +134,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -156,14 +141,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -172,7 +156,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -180,14 +163,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="O5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="O5" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -196,7 +178,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -218,15 +199,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{FCE6C7F4-D233-4863-A34C-A4F05704396F}">
+    <comment ref="F8" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -234,9 +213,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -246,15 +223,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{D09CD165-D541-4B41-810F-1A15102A61D4}">
+    <comment ref="O8" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -262,9 +237,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -296,6 +269,9 @@
     <t>倍场名称</t>
   </si>
   <si>
+    <t>参数-信息</t>
+  </si>
+  <si>
     <t>单线押分值</t>
   </si>
   <si>
@@ -308,6 +284,12 @@
     <t>押注进入标准池万分比</t>
   </si>
   <si>
+    <t>机器人加入房间间隔（毫秒）</t>
+  </si>
+  <si>
+    <t>机器人人数（时间段:机器人人数|……）</t>
+  </si>
+  <si>
     <t>跑马触发金额</t>
   </si>
   <si>
@@ -323,12 +305,18 @@
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{,}</t>
+  </si>
+  <si>
     <t>List&lt;int&gt;{_}</t>
   </si>
   <si>
     <t>long</t>
   </si>
   <si>
+    <t>list&lt;list&lt;int&gt;{:}&gt;{|}</t>
+  </si>
+  <si>
     <t>List&lt;long&gt;{_}</t>
   </si>
   <si>
@@ -344,6 +332,9 @@
     <t>roomName</t>
   </si>
   <si>
+    <t>information</t>
+  </si>
+  <si>
     <t>lineBetScore</t>
   </si>
   <si>
@@ -356,6 +347,12 @@
     <t>initBasePoolProportion</t>
   </si>
   <si>
+    <t>IntervalTime</t>
+  </si>
+  <si>
+    <t>robot_num</t>
+  </si>
+  <si>
     <t>marqueeTrigger</t>
   </si>
   <si>
@@ -389,53 +386,30 @@
     <t>空袭</t>
   </si>
   <si>
-    <t>list&lt;int&gt;{,}</t>
-  </si>
-  <si>
-    <t>1000,7000,5000,0</t>
-  </si>
-  <si>
-    <t>机器人加入房间间隔（毫秒）</t>
-  </si>
-  <si>
-    <t>机器人人数（时间段:机器人人数|……）</t>
-  </si>
-  <si>
-    <t>list&lt;list&lt;int&gt;{:}&gt;{|}</t>
-  </si>
-  <si>
-    <t>IntervalTime</t>
-  </si>
-  <si>
-    <t>robot_num</t>
+    <t>7000,1000,5000</t>
   </si>
   <si>
     <t>200,2000</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>0:6:3|6:12:2|12:18:2|18:24:3</t>
   </si>
   <si>
     <t>0_1200|1_60|2_300</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数-信息</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>information</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,86 +420,200 @@
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -534,19 +622,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7993408001953185"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7993408001953185"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7993408001953185"/>
+        <fgColor theme="7" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,12 +652,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -586,12 +860,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -609,19 +1125,22 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -630,6 +1149,12 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -639,52 +1164,90 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -962,12 +1525,12 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
@@ -983,7 +1546,7 @@
     <col min="15" max="15" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="18" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -999,381 +1562,381 @@
       <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:19">
+      <c r="A5" s="16">
+        <v>4002004</v>
+      </c>
+      <c r="B5" s="16">
+        <v>400200</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="16">
+        <v>400200001</v>
+      </c>
+      <c r="E5" s="16">
+        <v>4</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="16">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="16">
+        <v>10000000</v>
+      </c>
+      <c r="J5" s="16">
+        <v>9500</v>
+      </c>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="16">
+        <v>300</v>
+      </c>
+      <c r="Q5" s="16"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:19">
+      <c r="A6" s="16">
+        <v>4007004</v>
+      </c>
+      <c r="B6" s="16">
+        <v>400700</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="16">
+        <v>400700001</v>
+      </c>
+      <c r="E6" s="16">
+        <v>4</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="16">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="16">
+        <v>10000000</v>
+      </c>
+      <c r="J6" s="16">
+        <v>9500</v>
+      </c>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="16">
+        <v>9800</v>
+      </c>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:19">
+      <c r="A7" s="16">
+        <v>4005004</v>
+      </c>
+      <c r="B7" s="16">
+        <v>400500</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="16">
+        <v>400500001</v>
+      </c>
+      <c r="E7" s="16">
+        <v>4</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="16">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="16">
+        <v>10000000</v>
+      </c>
+      <c r="J7" s="16">
+        <v>9500</v>
+      </c>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" s="16">
+        <v>9600</v>
+      </c>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:19">
+      <c r="A8" s="16">
+        <v>4004004</v>
+      </c>
+      <c r="B8" s="16">
+        <v>400400</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="16">
+        <v>400400001</v>
+      </c>
+      <c r="E8" s="16">
+        <v>4</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="16">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="16">
+        <v>10000000</v>
+      </c>
+      <c r="J8" s="16">
+        <v>9500</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="21" t="s">
+      <c r="M8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="P8" s="16">
+        <v>300</v>
+      </c>
+      <c r="Q8" s="16"/>
     </row>
-    <row r="2" spans="1:19" s="2" customFormat="1" ht="16.5">
-      <c r="A2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
+    <row r="9" ht="16.5" spans="1:19">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
     </row>
-    <row r="3" spans="1:19" s="2" customFormat="1" ht="16.5">
-      <c r="A3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
+    <row r="13" ht="16.5" spans="1:19">
+      <c r="G13" s="25"/>
     </row>
-    <row r="4" spans="1:19" s="2" customFormat="1" ht="16.5">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
+    <row r="14" ht="16.5" spans="1:19">
+      <c r="G14" s="25"/>
     </row>
-    <row r="5" spans="1:19" ht="16.5">
-      <c r="A5" s="13">
-        <v>4002004</v>
-      </c>
-      <c r="B5" s="13">
-        <v>400200</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="13">
-        <v>400200001</v>
-      </c>
-      <c r="E5" s="13">
-        <v>4</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="13">
-        <v>1000</v>
-      </c>
-      <c r="I5" s="13">
-        <v>10000000</v>
-      </c>
-      <c r="J5" s="13">
-        <v>9500</v>
-      </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="P5" s="13">
-        <v>300</v>
-      </c>
-      <c r="Q5" s="13"/>
+    <row r="15" ht="16.5" spans="1:19">
+      <c r="G15" s="25"/>
     </row>
-    <row r="6" spans="1:19" ht="16.5">
-      <c r="A6" s="13">
-        <v>4007004</v>
-      </c>
-      <c r="B6" s="13">
-        <v>400700</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="13">
-        <v>400700001</v>
-      </c>
-      <c r="E6" s="13">
-        <v>4</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="13">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="13">
-        <v>10000000</v>
-      </c>
-      <c r="J6" s="13">
-        <v>9500</v>
-      </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="13">
-        <v>9800</v>
-      </c>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
+    <row r="16" ht="16.5" spans="1:19">
+      <c r="G16" s="25"/>
     </row>
-    <row r="7" spans="1:19" ht="16.5">
-      <c r="A7" s="13">
-        <v>4005004</v>
-      </c>
-      <c r="B7" s="13">
-        <v>400500</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="13">
-        <v>400500001</v>
-      </c>
-      <c r="E7" s="13">
-        <v>4</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="13">
-        <v>1000</v>
-      </c>
-      <c r="I7" s="13">
-        <v>10000000</v>
-      </c>
-      <c r="J7" s="13">
-        <v>9500</v>
-      </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="13">
-        <v>9600</v>
-      </c>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
+    <row r="17" ht="16.5" spans="7:7">
+      <c r="G17" s="25"/>
     </row>
-    <row r="8" spans="1:19" ht="16.5">
-      <c r="A8" s="13">
-        <v>4004004</v>
-      </c>
-      <c r="B8" s="13">
-        <v>400400</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="13">
-        <v>400400001</v>
-      </c>
-      <c r="E8" s="13">
-        <v>4</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="13">
-        <v>1000</v>
-      </c>
-      <c r="I8" s="13">
-        <v>10000000</v>
-      </c>
-      <c r="J8" s="13">
-        <v>9500</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8" s="13">
-        <v>300</v>
-      </c>
-      <c r="Q8" s="13"/>
+    <row r="18" ht="16.5" spans="7:7">
+      <c r="G18" s="25"/>
     </row>
-    <row r="9" spans="1:19" ht="16.5">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-    </row>
-    <row r="13" spans="1:19" ht="16.5">
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:19" ht="16.5">
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" spans="1:19" ht="16.5">
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:19" ht="16.5">
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="7:7" ht="16.5">
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" spans="7:7" ht="16.5">
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="7:7" ht="16.5">
-      <c r="G19" s="18"/>
+    <row r="19" ht="16.5" spans="7:7">
+      <c r="G19" s="25"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>